--- a/Team-Data/2013-14/4-1-2013-14.xlsx
+++ b/Team-Data/2013-14/4-1-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>-1.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE2" t="n">
         <v>18</v>
@@ -763,7 +830,7 @@
         <v>13</v>
       </c>
       <c r="AL2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM2" t="n">
         <v>2</v>
@@ -775,7 +842,7 @@
         <v>17</v>
       </c>
       <c r="AP2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ2" t="n">
         <v>8</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-1-2013-14</t>
+          <t>2014-04-01</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-4.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE3" t="n">
         <v>26</v>
@@ -975,7 +1042,7 @@
         <v>25</v>
       </c>
       <c r="AV3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW3" t="n">
         <v>23</v>
@@ -984,7 +1051,7 @@
         <v>21</v>
       </c>
       <c r="AY3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ3" t="n">
         <v>19</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-1-2013-14</t>
+          <t>2014-04-01</t>
         </is>
       </c>
     </row>
@@ -1025,55 +1092,55 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E4" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F4" t="n">
         <v>33</v>
       </c>
       <c r="G4" t="n">
-        <v>0.548</v>
+        <v>0.542</v>
       </c>
       <c r="H4" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="J4" t="n">
-        <v>78.3</v>
+        <v>78.2</v>
       </c>
       <c r="K4" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L4" t="n">
         <v>8.6</v>
       </c>
       <c r="M4" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.37</v>
+        <v>0.372</v>
       </c>
       <c r="O4" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="P4" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.759</v>
+        <v>0.76</v>
       </c>
       <c r="R4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="S4" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="T4" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="U4" t="n">
         <v>20.8</v>
@@ -1091,19 +1158,19 @@
         <v>4.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>98.8</v>
+        <v>98.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AE4" t="n">
         <v>14</v>
@@ -1133,13 +1200,13 @@
         <v>10</v>
       </c>
       <c r="AN4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AO4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ4" t="n">
         <v>15</v>
@@ -1160,7 +1227,7 @@
         <v>10</v>
       </c>
       <c r="AW4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX4" t="n">
         <v>27</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-1-2013-14</t>
+          <t>2014-04-01</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-1</v>
       </c>
       <c r="AD5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE5" t="n">
         <v>16</v>
@@ -1345,7 +1412,7 @@
         <v>29</v>
       </c>
       <c r="AX5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY5" t="n">
         <v>20</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-1-2013-14</t>
+          <t>2014-04-01</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>1.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE6" t="n">
         <v>12</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-1-2013-14</t>
+          <t>2014-04-01</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-4.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
         <v>22</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-1-2013-14</t>
+          <t>2014-04-01</t>
         </is>
       </c>
     </row>
@@ -1753,25 +1820,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E8" t="n">
         <v>44</v>
       </c>
       <c r="F8" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G8" t="n">
-        <v>0.587</v>
+        <v>0.595</v>
       </c>
       <c r="H8" t="n">
         <v>48.3</v>
       </c>
       <c r="I8" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="J8" t="n">
-        <v>83.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K8" t="n">
         <v>0.473</v>
@@ -1780,67 +1847,67 @@
         <v>8.699999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0.384</v>
+        <v>0.383</v>
       </c>
       <c r="O8" t="n">
         <v>17.3</v>
       </c>
       <c r="P8" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.796</v>
+        <v>0.797</v>
       </c>
       <c r="R8" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="S8" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="T8" t="n">
         <v>40.7</v>
       </c>
       <c r="U8" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="V8" t="n">
         <v>13.6</v>
       </c>
       <c r="W8" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y8" t="n">
         <v>3.6</v>
       </c>
       <c r="Z8" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="AA8" t="n">
         <v>20.2</v>
       </c>
-      <c r="AA8" t="n">
-        <v>20.1</v>
-      </c>
       <c r="AB8" t="n">
-        <v>105.1</v>
+        <v>104.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
       </c>
       <c r="AF8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AH8" t="n">
         <v>19</v>
@@ -1897,7 +1964,7 @@
         <v>3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA8" t="n">
         <v>20</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-1-2013-14</t>
+          <t>2014-04-01</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-2.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE9" t="n">
         <v>18</v>
@@ -2073,7 +2140,7 @@
         <v>17</v>
       </c>
       <c r="AX9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY9" t="n">
         <v>25</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-1-2013-14</t>
+          <t>2014-04-01</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-3.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2207,10 +2274,10 @@
         <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ10" t="n">
         <v>4</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-1-2013-14</t>
+          <t>2014-04-01</t>
         </is>
       </c>
     </row>
@@ -2299,46 +2366,46 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F11" t="n">
         <v>28</v>
       </c>
       <c r="G11" t="n">
-        <v>0.622</v>
+        <v>0.616</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>39</v>
+        <v>38.8</v>
       </c>
       <c r="J11" t="n">
-        <v>84.8</v>
+        <v>84.7</v>
       </c>
       <c r="K11" t="n">
-        <v>0.46</v>
+        <v>0.458</v>
       </c>
       <c r="L11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="M11" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="N11" t="n">
-        <v>0.376</v>
+        <v>0.374</v>
       </c>
       <c r="O11" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="P11" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.752</v>
+        <v>0.753</v>
       </c>
       <c r="R11" t="n">
         <v>11</v>
@@ -2350,7 +2417,7 @@
         <v>45.3</v>
       </c>
       <c r="U11" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="V11" t="n">
         <v>15.3</v>
@@ -2359,25 +2426,25 @@
         <v>7.6</v>
       </c>
       <c r="X11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y11" t="n">
         <v>4.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>103.4</v>
+        <v>103.2</v>
       </c>
       <c r="AC11" t="n">
         <v>4.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2392,31 +2459,31 @@
         <v>18</v>
       </c>
       <c r="AI11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK11" t="n">
         <v>10</v>
       </c>
       <c r="AL11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN11" t="n">
         <v>5</v>
       </c>
       <c r="AO11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AP11" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AQ11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR11" t="n">
         <v>16</v>
@@ -2431,13 +2498,13 @@
         <v>9</v>
       </c>
       <c r="AV11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW11" t="n">
         <v>14</v>
       </c>
       <c r="AX11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-1-2013-14</t>
+          <t>2014-04-01</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E12" t="n">
         <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G12" t="n">
-        <v>0.671</v>
+        <v>0.681</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
@@ -2502,16 +2569,16 @@
         <v>79.8</v>
       </c>
       <c r="K12" t="n">
-        <v>0.474</v>
+        <v>0.476</v>
       </c>
       <c r="L12" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0.354</v>
+        <v>0.356</v>
       </c>
       <c r="O12" t="n">
         <v>21.8</v>
@@ -2520,7 +2587,7 @@
         <v>31</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.704</v>
+        <v>0.703</v>
       </c>
       <c r="R12" t="n">
         <v>11.2</v>
@@ -2553,19 +2620,19 @@
         <v>24.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>106.8</v>
+        <v>107</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AE12" t="n">
         <v>6</v>
       </c>
       <c r="AF12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG12" t="n">
         <v>6</v>
@@ -2580,7 +2647,7 @@
         <v>28</v>
       </c>
       <c r="AK12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL12" t="n">
         <v>5</v>
@@ -2607,10 +2674,10 @@
         <v>5</v>
       </c>
       <c r="AT12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
@@ -2625,16 +2692,16 @@
         <v>22</v>
       </c>
       <c r="AZ12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
       </c>
       <c r="BB12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-1-2013-14</t>
+          <t>2014-04-01</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>4.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE13" t="n">
         <v>4</v>
@@ -2807,7 +2874,7 @@
         <v>15</v>
       </c>
       <c r="AZ13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA13" t="n">
         <v>5</v>
@@ -2816,7 +2883,7 @@
         <v>24</v>
       </c>
       <c r="BC13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-1-2013-14</t>
+          <t>2014-04-01</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>7.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2944,7 +3011,7 @@
         <v>20</v>
       </c>
       <c r="AK14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL14" t="n">
         <v>11</v>
@@ -2980,7 +3047,7 @@
         <v>8</v>
       </c>
       <c r="AW14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX14" t="n">
         <v>13</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-1-2013-14</t>
+          <t>2014-04-01</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E15" t="n">
         <v>25</v>
       </c>
       <c r="F15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G15" t="n">
-        <v>0.338</v>
+        <v>0.342</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
@@ -3045,19 +3112,19 @@
         <v>38.2</v>
       </c>
       <c r="J15" t="n">
-        <v>84.8</v>
+        <v>84.7</v>
       </c>
       <c r="K15" t="n">
         <v>0.45</v>
       </c>
       <c r="L15" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M15" t="n">
         <v>24.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0.384</v>
+        <v>0.383</v>
       </c>
       <c r="O15" t="n">
         <v>16.9</v>
@@ -3066,7 +3133,7 @@
         <v>22.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.754</v>
+        <v>0.753</v>
       </c>
       <c r="R15" t="n">
         <v>9.199999999999999</v>
@@ -3078,16 +3145,16 @@
         <v>41.1</v>
       </c>
       <c r="U15" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="V15" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W15" t="n">
         <v>7.3</v>
       </c>
       <c r="X15" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y15" t="n">
         <v>4.6</v>
@@ -3099,19 +3166,19 @@
         <v>19.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.7</v>
+        <v>102.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.2</v>
+        <v>-6.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
       </c>
       <c r="AF15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG15" t="n">
         <v>25</v>
@@ -3132,7 +3199,7 @@
         <v>4</v>
       </c>
       <c r="AM15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN15" t="n">
         <v>4</v>
@@ -3144,7 +3211,7 @@
         <v>19</v>
       </c>
       <c r="AQ15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR15" t="n">
         <v>26</v>
@@ -3165,13 +3232,13 @@
         <v>20</v>
       </c>
       <c r="AX15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY15" t="n">
         <v>13</v>
       </c>
       <c r="AZ15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-1-2013-14</t>
+          <t>2014-04-01</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>1.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE16" t="n">
         <v>9</v>
@@ -3299,7 +3366,7 @@
         <v>9</v>
       </c>
       <c r="AH16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI16" t="n">
         <v>16</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-1-2013-14</t>
+          <t>2014-04-01</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>5.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE17" t="n">
         <v>5</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-1-2013-14</t>
+          <t>2014-04-01</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3684,7 +3751,7 @@
         <v>18</v>
       </c>
       <c r="AO18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP18" t="n">
         <v>20</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-1-2013-14</t>
+          <t>2014-04-01</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>3.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE19" t="n">
         <v>16</v>
@@ -3848,7 +3915,7 @@
         <v>23</v>
       </c>
       <c r="AI19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ19" t="n">
         <v>2</v>
@@ -3887,7 +3954,7 @@
         <v>5</v>
       </c>
       <c r="AV19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW19" t="n">
         <v>4</v>
@@ -3905,7 +3972,7 @@
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-1-2013-14</t>
+          <t>2014-04-01</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE20" t="n">
         <v>18</v>
@@ -4045,7 +4112,7 @@
         <v>29</v>
       </c>
       <c r="AN20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO20" t="n">
         <v>12</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-1-2013-14</t>
+          <t>2014-04-01</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-1.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE21" t="n">
         <v>18</v>
@@ -4221,13 +4288,13 @@
         <v>18</v>
       </c>
       <c r="AL21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM21" t="n">
         <v>5</v>
       </c>
       <c r="AN21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-1-2013-14</t>
+          <t>2014-04-01</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>6.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4391,7 +4458,7 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI22" t="n">
         <v>4</v>
@@ -4427,7 +4494,7 @@
         <v>3</v>
       </c>
       <c r="AT22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU22" t="n">
         <v>13</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-1-2013-14</t>
+          <t>2014-04-01</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-5.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE23" t="n">
         <v>28</v>
@@ -4618,7 +4685,7 @@
         <v>14</v>
       </c>
       <c r="AW23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX23" t="n">
         <v>24</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-1-2013-14</t>
+          <t>2014-04-01</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-11</v>
       </c>
       <c r="AD24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4776,7 +4843,7 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP24" t="n">
         <v>17</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-1-2013-14</t>
+          <t>2014-04-01</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>2.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE25" t="n">
         <v>9</v>
@@ -4949,7 +5016,7 @@
         <v>8</v>
       </c>
       <c r="AL25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM25" t="n">
         <v>4</v>
@@ -4958,10 +5025,10 @@
         <v>6</v>
       </c>
       <c r="AO25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ25" t="n">
         <v>16</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-1-2013-14</t>
+          <t>2014-04-01</t>
         </is>
       </c>
     </row>
@@ -5029,37 +5096,37 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E26" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F26" t="n">
         <v>27</v>
       </c>
       <c r="G26" t="n">
-        <v>0.645</v>
+        <v>0.64</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>39.1</v>
+        <v>39</v>
       </c>
       <c r="J26" t="n">
-        <v>87.09999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L26" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="M26" t="n">
         <v>25.4</v>
       </c>
       <c r="N26" t="n">
-        <v>0.373</v>
+        <v>0.372</v>
       </c>
       <c r="O26" t="n">
         <v>19.3</v>
@@ -5068,49 +5135,49 @@
         <v>23.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.82</v>
+        <v>0.819</v>
       </c>
       <c r="R26" t="n">
         <v>12.5</v>
       </c>
       <c r="S26" t="n">
-        <v>33.8</v>
+        <v>33.7</v>
       </c>
       <c r="T26" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
       <c r="U26" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="V26" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="W26" t="n">
         <v>5.5</v>
       </c>
       <c r="X26" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>106.8</v>
+        <v>106.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AD26" t="n">
         <v>1</v>
       </c>
       <c r="AE26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF26" t="n">
         <v>7</v>
@@ -5128,10 +5195,10 @@
         <v>3</v>
       </c>
       <c r="AK26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AM26" t="n">
         <v>3</v>
@@ -5158,10 +5225,10 @@
         <v>1</v>
       </c>
       <c r="AU26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW26" t="n">
         <v>30</v>
@@ -5179,7 +5246,7 @@
         <v>11</v>
       </c>
       <c r="BB26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BC26" t="n">
         <v>8</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-1-2013-14</t>
+          <t>2014-04-01</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-2.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
@@ -5310,7 +5377,7 @@
         <v>19</v>
       </c>
       <c r="AK27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL27" t="n">
         <v>25</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-1-2013-14</t>
+          <t>2014-04-01</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>8.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5513,7 +5580,7 @@
         <v>4</v>
       </c>
       <c r="AR28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS28" t="n">
         <v>4</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-1-2013-14</t>
+          <t>2014-04-01</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>3.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE29" t="n">
         <v>12</v>
@@ -5704,7 +5771,7 @@
         <v>17</v>
       </c>
       <c r="AU29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV29" t="n">
         <v>9</v>
@@ -5713,7 +5780,7 @@
         <v>23</v>
       </c>
       <c r="AX29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY29" t="n">
         <v>11</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-1-2013-14</t>
+          <t>2014-04-01</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-7</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE30" t="n">
         <v>26</v>
@@ -5871,7 +5938,7 @@
         <v>24</v>
       </c>
       <c r="AP30" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AQ30" t="n">
         <v>22</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-1-2013-14</t>
+          <t>2014-04-01</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>0.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE31" t="n">
         <v>15</v>
@@ -6035,7 +6102,7 @@
         <v>11</v>
       </c>
       <c r="AJ31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK31" t="n">
         <v>12</v>
@@ -6068,7 +6135,7 @@
         <v>19</v>
       </c>
       <c r="AU31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV31" t="n">
         <v>15</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-1-2013-14</t>
+          <t>2014-04-01</t>
         </is>
       </c>
     </row>
